--- a/data/raw/IPC.xlsx
+++ b/data/raw/IPC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sriverti\Desktop\INECO\Repositorios\cuentas_publicas\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D26A2E2-D630-4A1B-B5C2-1E23A046A739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664201AB-176B-4ED0-8AE6-D60C11C57200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
     <numFmt numFmtId="164" formatCode="mmm&quot;-&quot;yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -129,8 +129,21 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,8 +156,14 @@
         <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -168,11 +187,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -207,10 +241,13 @@
     <xf numFmtId="2" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5439,7 +5476,7 @@
       </c>
       <c r="O111" s="9"/>
     </row>
-    <row r="112" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10">
         <v>46082</v>
       </c>
@@ -5484,56 +5521,228 @@
       </c>
       <c r="O112" s="9"/>
     </row>
-    <row r="113" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="10">
+    <row r="113" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="13">
         <v>46113</v>
       </c>
-      <c r="B113" s="12">
+      <c r="B113" s="14">
         <v>11363.09</v>
       </c>
-      <c r="C113" s="12">
+      <c r="C113" s="14">
         <v>12194.882</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="14">
         <v>7969.9790000000003</v>
       </c>
-      <c r="E113" s="12">
+      <c r="E113" s="14">
         <v>8326.6610000000001</v>
       </c>
-      <c r="F113" s="12">
+      <c r="F113" s="14">
         <v>12470.696</v>
       </c>
-      <c r="G113" s="12">
+      <c r="G113" s="14">
         <v>9182.7939999999999</v>
       </c>
-      <c r="H113" s="12">
+      <c r="H113" s="14">
         <v>12508.39</v>
       </c>
-      <c r="I113" s="12">
+      <c r="I113" s="14">
         <v>12091.593000000001</v>
       </c>
-      <c r="J113" s="12">
+      <c r="J113" s="14">
         <v>10478.731</v>
       </c>
-      <c r="K113" s="12">
+      <c r="K113" s="14">
         <v>9860.2729999999992</v>
       </c>
-      <c r="L113" s="12">
+      <c r="L113" s="14">
         <v>10532.134</v>
       </c>
-      <c r="M113" s="12">
+      <c r="M113" s="14">
         <v>14041.197</v>
       </c>
-      <c r="N113" s="12">
+      <c r="N113" s="14">
         <v>10914.151</v>
       </c>
       <c r="O113" s="9"/>
-      <c r="P113" s="13"/>
-    </row>
-    <row r="114" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="P113" s="12"/>
+    </row>
+    <row r="114" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="13">
+        <v>46143</v>
+      </c>
+      <c r="B114" s="14">
+        <v>11607.39</v>
+      </c>
+      <c r="C114" s="14">
+        <v>12494.98</v>
+      </c>
+      <c r="D114" s="14">
+        <v>8033.26</v>
+      </c>
+      <c r="E114" s="14">
+        <v>8350.24</v>
+      </c>
+      <c r="F114" s="14">
+        <v>12790.08</v>
+      </c>
+      <c r="G114" s="14">
+        <v>9312.2099999999991</v>
+      </c>
+      <c r="H114" s="14">
+        <v>12832.03</v>
+      </c>
+      <c r="I114" s="14">
+        <v>12330.5</v>
+      </c>
+      <c r="J114" s="14">
+        <v>10838.43</v>
+      </c>
+      <c r="K114" s="14">
+        <v>10132.370000000001</v>
+      </c>
+      <c r="L114" s="14">
+        <v>10840.93</v>
+      </c>
+      <c r="M114" s="14">
+        <v>14291.48</v>
+      </c>
+      <c r="N114" s="14">
+        <v>11171.62</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="13">
+        <v>46174</v>
+      </c>
+      <c r="B115" s="14">
+        <v>11826.41</v>
+      </c>
+      <c r="C115" s="14">
+        <v>12657.46</v>
+      </c>
+      <c r="D115" s="14">
+        <v>8201.66</v>
+      </c>
+      <c r="E115" s="14">
+        <v>8384.7199999999993</v>
+      </c>
+      <c r="F115" s="14">
+        <v>13213.15</v>
+      </c>
+      <c r="G115" s="14">
+        <v>9455.0400000000009</v>
+      </c>
+      <c r="H115" s="14">
+        <v>13200.75</v>
+      </c>
+      <c r="I115" s="14">
+        <v>12531.8</v>
+      </c>
+      <c r="J115" s="14">
+        <v>10933.56</v>
+      </c>
+      <c r="K115" s="14">
+        <v>10556.46</v>
+      </c>
+      <c r="L115" s="14">
+        <v>11025.4</v>
+      </c>
+      <c r="M115" s="14">
+        <v>14524.08</v>
+      </c>
+      <c r="N115" s="14">
+        <v>11373.14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="13">
+        <v>46204</v>
+      </c>
+      <c r="B116" s="14">
+        <v>12076.39</v>
+      </c>
+      <c r="C116" s="14">
+        <v>12907.51</v>
+      </c>
+      <c r="D116" s="14">
+        <v>8325.6</v>
+      </c>
+      <c r="E116" s="14">
+        <v>8272.2800000000007</v>
+      </c>
+      <c r="F116" s="14">
+        <v>13505.36</v>
+      </c>
+      <c r="G116" s="14">
+        <v>9653.7199999999993</v>
+      </c>
+      <c r="H116" s="14">
+        <v>13536.83</v>
+      </c>
+      <c r="I116" s="14">
+        <v>12767.66</v>
+      </c>
+      <c r="J116" s="14">
+        <v>11194.26</v>
+      </c>
+      <c r="K116" s="14">
+        <v>11085.75</v>
+      </c>
+      <c r="L116" s="14">
+        <v>11235.67</v>
+      </c>
+      <c r="M116" s="14">
+        <v>14923.82</v>
+      </c>
+      <c r="N116" s="14">
+        <v>11628.31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="13">
+        <v>46235</v>
+      </c>
+      <c r="B117" s="14">
+        <v>12276.77</v>
+      </c>
+      <c r="C117" s="14">
+        <v>13121.25</v>
+      </c>
+      <c r="D117" s="14">
+        <v>8502.1200000000008</v>
+      </c>
+      <c r="E117" s="14">
+        <v>8218.76</v>
+      </c>
+      <c r="F117" s="14">
+        <v>13885.49</v>
+      </c>
+      <c r="G117" s="14">
+        <v>9793.69</v>
+      </c>
+      <c r="H117" s="14">
+        <v>13863.05</v>
+      </c>
+      <c r="I117" s="14">
+        <v>12965.12</v>
+      </c>
+      <c r="J117" s="14">
+        <v>11449.47</v>
+      </c>
+      <c r="K117" s="14">
+        <v>11084.1</v>
+      </c>
+      <c r="L117" s="14">
+        <v>11519.72</v>
+      </c>
+      <c r="M117" s="14">
+        <v>15196.18</v>
+      </c>
+      <c r="N117" s="14">
+        <v>11911.9</v>
+      </c>
+    </row>
     <row r="118" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="119" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="120" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
